--- a/aReport_card/2025_2026/Second_term/JSS1/Second_term_JSS1_Christianity_Religious_Studies.xlsx
+++ b/aReport_card/2025_2026/Second_term/JSS1/Second_term_JSS1_Christianity_Religious_Studies.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B931408D-B334-4338-9FF4-39D365D17F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B5711E-3214-459A-A616-9671090E51C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -541,14 +541,10 @@
         <v>33</v>
       </c>
       <c r="D4" s="1">
-        <v>28</v>
-      </c>
-      <c r="E4" s="1">
-        <v>15</v>
-      </c>
-      <c r="F4" s="1">
-        <v>76</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
